--- a/new-stats/henan-fc.xlsx
+++ b/new-stats/henan-fc.xlsx
@@ -2077,22 +2077,62 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Henan FC</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Tianjin Jinmen Tiger</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="M29" t="n">
+        <v>14</v>
+      </c>
+      <c r="N29" t="n">
+        <v>5</v>
+      </c>
+      <c r="O29" t="n">
+        <v>3</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>

--- a/new-stats/henan-fc.xlsx
+++ b/new-stats/henan-fc.xlsx
@@ -2135,22 +2135,62 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>24/10/2026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Henan FC</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" t="n">
+        <v>4</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Beijing Guoan</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>3</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>4</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="L30" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="M30" t="n">
+        <v>15</v>
+      </c>
+      <c r="N30" t="n">
+        <v>12</v>
+      </c>
+      <c r="O30" t="n">
+        <v>7</v>
+      </c>
+      <c r="P30" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
